--- a/接口文档/上清接口文档.xlsx
+++ b/接口文档/上清接口文档.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="14780" firstSheet="4"/>
+    <workbookView windowWidth="18240" windowHeight="8360" firstSheet="4" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="8" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="422">
   <si>
     <t>接口名称</t>
   </si>
@@ -2501,14 +2501,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
-    <col min="2" max="2" width="51.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.7211538461538" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5044247787611" customWidth="1"/>
+    <col min="2" max="2" width="51.3716814159292" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.716814159292" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" spans="1:3">
+    <row r="1" ht="23" spans="1:3">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
@@ -2519,14 +2519,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:3">
+    <row r="2" ht="20.65" spans="1:3">
       <c r="A2" s="39" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
     </row>
-    <row r="3" ht="14.3" customHeight="1" spans="1:3">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="41" t="s">
         <v>4</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="14.3" customHeight="1" spans="1:3">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="41" t="s">
         <v>6</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="23.2" spans="1:3">
+    <row r="5" ht="20.65" spans="1:3">
       <c r="A5" s="39" t="s">
         <v>8</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="14.3" customHeight="1" spans="1:3">
+    <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="41" t="s">
         <v>13</v>
       </c>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C8" s="39"/>
     </row>
-    <row r="9" ht="23.2" spans="1:3">
+    <row r="9" ht="20.65" spans="1:3">
       <c r="A9" s="39" t="s">
         <v>15</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="23.2" spans="1:3">
+    <row r="13" ht="20.65" spans="1:3">
       <c r="A13" s="39" t="s">
         <v>19</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="23.2" spans="1:3">
+    <row r="17" ht="20.65" spans="1:3">
       <c r="A17" s="39" t="s">
         <v>23</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" ht="23.2" spans="1:3">
+    <row r="19" ht="20.65" spans="1:3">
       <c r="A19" s="39" t="s">
         <v>25</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" ht="23.2" spans="1:3">
+    <row r="21" ht="20.65" spans="1:3">
       <c r="A21" s="39" t="s">
         <v>27</v>
       </c>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C22" s="42"/>
     </row>
-    <row r="23" ht="23.2" spans="1:3">
+    <row r="23" ht="20.65" spans="1:3">
       <c r="A23" s="39" t="s">
         <v>29</v>
       </c>
@@ -2769,15 +2769,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="42.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.375" customWidth="1"/>
+    <col min="1" max="1" width="42.6283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1238938053097" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.3716814159292" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" spans="1:8">
+    <row r="1" ht="23" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:8">
+    <row r="2" ht="20.65" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
@@ -2802,7 +2802,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" ht="20.4" spans="1:8">
+    <row r="3" ht="17.65" spans="1:8">
       <c r="A3" s="19" t="s">
         <v>46</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="20.4" spans="1:8">
+    <row r="5" ht="17.65" spans="1:8">
       <c r="A5" s="19" t="s">
         <v>48</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" ht="23.2" spans="1:4">
+    <row r="31" ht="20.65" spans="1:4">
       <c r="A31" s="8" t="s">
         <v>6</v>
       </c>
@@ -3095,7 +3095,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" ht="20.4" spans="1:4">
+    <row r="32" ht="17.65" spans="1:4">
       <c r="A32" s="19" t="s">
         <v>46</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="20.4" spans="1:4">
+    <row r="34" ht="17.65" spans="1:4">
       <c r="A34" s="19" t="s">
         <v>48</v>
       </c>
@@ -3142,15 +3142,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H103"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="42.625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="27" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="28.375" style="29" customWidth="1"/>
+    <col min="1" max="1" width="42.6283185840708" style="27" customWidth="1"/>
+    <col min="2" max="2" width="9.75221238938053" style="27" customWidth="1"/>
+    <col min="3" max="3" width="38.1238938053097" style="27" customWidth="1"/>
+    <col min="4" max="4" width="28.3716814159292" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" spans="1:8">
+    <row r="1" ht="23" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:8">
+    <row r="2" ht="20.65" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -3175,7 +3175,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" ht="20.4" spans="1:8">
+    <row r="3" ht="17.65" spans="1:8">
       <c r="A3" s="19" t="s">
         <v>46</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" ht="51" spans="1:8">
+    <row r="5" ht="28.65" spans="1:8">
       <c r="A5" s="27" t="s">
         <v>102</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" ht="51" spans="1:8">
+    <row r="8" ht="28.65" spans="1:8">
       <c r="A8" s="27" t="s">
         <v>109</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" ht="51" spans="1:8">
+    <row r="10" ht="28.65" spans="1:8">
       <c r="A10" s="27" t="s">
         <v>114</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" ht="17" spans="1:8">
+    <row r="11" ht="14.35" spans="1:8">
       <c r="A11" s="27" t="s">
         <v>117</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" ht="17" spans="1:8">
+    <row r="12" ht="14.35" spans="1:8">
       <c r="A12" s="27" t="s">
         <v>120</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" ht="51" spans="1:8">
+    <row r="14" ht="28.65" spans="1:8">
       <c r="A14" s="27" t="s">
         <v>124</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" ht="51" spans="1:8">
+    <row r="15" ht="28.65" spans="1:8">
       <c r="A15" s="27" t="s">
         <v>126</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="16" ht="17" spans="1:8">
+    <row r="16" ht="14.35" spans="1:8">
       <c r="A16" s="27" t="s">
         <v>129</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" ht="17" spans="1:4">
+    <row r="17" ht="14.35" spans="1:4">
       <c r="A17" s="27" t="s">
         <v>131</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" ht="17" spans="1:4">
+    <row r="18" ht="14.35" spans="1:4">
       <c r="A18" s="27" t="s">
         <v>133</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:4">
+    <row r="19" ht="14.35" spans="1:4">
       <c r="A19" s="27" t="s">
         <v>135</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" ht="20.4" spans="1:4">
+    <row r="21" ht="17.65" spans="1:4">
       <c r="A21" s="19" t="s">
         <v>48</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="36" ht="23.2" spans="1:4">
+    <row r="36" ht="20.65" spans="1:4">
       <c r="A36" s="25" t="s">
         <v>11</v>
       </c>
@@ -3563,7 +3563,7 @@
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
     </row>
-    <row r="37" ht="20.4" spans="1:4">
+    <row r="37" ht="17.65" spans="1:4">
       <c r="A37" s="19" t="s">
         <v>46</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" ht="20.4" spans="1:4">
+    <row r="39" ht="17.65" spans="1:4">
       <c r="A39" s="19" t="s">
         <v>48</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="46" ht="17" spans="1:4">
+    <row r="46" ht="14.35" spans="1:4">
       <c r="A46" s="34" t="s">
         <v>167</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="78" ht="17" spans="1:3">
+    <row r="78" ht="14.35" spans="1:3">
       <c r="A78" s="34" t="s">
         <v>210</v>
       </c>
@@ -4088,7 +4088,7 @@
     <row r="85" spans="1:4">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" ht="23.2" spans="1:4">
+    <row r="86" ht="20.65" spans="1:4">
       <c r="A86" s="26" t="s">
         <v>13</v>
       </c>
@@ -4096,7 +4096,7 @@
       <c r="C86" s="26"/>
       <c r="D86" s="26"/>
     </row>
-    <row r="87" ht="20.4" spans="1:4">
+    <row r="87" ht="17.65" spans="1:4">
       <c r="A87" s="19" t="s">
         <v>46</v>
       </c>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="D88"/>
     </row>
-    <row r="89" ht="20.4" spans="1:4">
+    <row r="89" ht="17.65" spans="1:4">
       <c r="A89" s="19" t="s">
         <v>48</v>
       </c>
@@ -4291,15 +4291,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="42.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.375" customWidth="1"/>
+    <col min="1" max="1" width="42.6283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1238938053097" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.3716814159292" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" spans="1:8">
+    <row r="1" ht="23" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:8">
+    <row r="2" ht="20.65" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -4324,7 +4324,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" ht="20.4" spans="1:8">
+    <row r="3" ht="17.65" spans="1:8">
       <c r="A3" s="19" t="s">
         <v>46</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" ht="51" spans="1:8">
+    <row r="6" ht="28.65" spans="1:8">
       <c r="A6" s="16" t="s">
         <v>159</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" ht="51" spans="1:8">
+    <row r="7" ht="28.65" spans="1:8">
       <c r="A7" s="16" t="s">
         <v>102</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" ht="51" spans="1:8">
+    <row r="8" spans="1:8">
       <c r="A8" s="16" t="s">
         <v>105</v>
       </c>
@@ -4392,11 +4392,9 @@
       <c r="C8" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" ht="51" spans="1:8">
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" ht="28.65" spans="1:8">
       <c r="A9" s="16" t="s">
         <v>114</v>
       </c>
@@ -4432,7 +4430,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" ht="17" spans="1:8">
+    <row r="12" ht="14.35" spans="1:8">
       <c r="A12" s="16" t="s">
         <v>117</v>
       </c>
@@ -4446,7 +4444,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="1:8">
+    <row r="13" ht="14.35" spans="1:8">
       <c r="A13" s="16" t="s">
         <v>120</v>
       </c>
@@ -4460,7 +4458,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:8">
+    <row r="14" ht="14.35" spans="1:8">
       <c r="A14" s="16" t="s">
         <v>241</v>
       </c>
@@ -4474,7 +4472,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:8">
+    <row r="15" ht="14.35" spans="1:8">
       <c r="A15" s="16" t="s">
         <v>243</v>
       </c>
@@ -4488,7 +4486,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" ht="20.4" spans="1:8">
+    <row r="16" ht="17.65" spans="1:8">
       <c r="A16" s="19" t="s">
         <v>48</v>
       </c>
@@ -4859,7 +4857,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="51" ht="23.2" spans="1:4">
+    <row r="51" ht="20.65" spans="1:4">
       <c r="A51" s="25" t="s">
         <v>11</v>
       </c>
@@ -4867,7 +4865,7 @@
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
     </row>
-    <row r="52" ht="20.4" spans="1:4">
+    <row r="52" ht="17.65" spans="1:4">
       <c r="A52" s="19" t="s">
         <v>46</v>
       </c>
@@ -4886,7 +4884,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" ht="20.4" spans="1:4">
+    <row r="54" ht="17.65" spans="1:4">
       <c r="A54" s="19" t="s">
         <v>48</v>
       </c>
@@ -5224,7 +5222,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="86" ht="23.2" spans="1:4">
+    <row r="86" ht="20.65" spans="1:4">
       <c r="A86" s="26" t="s">
         <v>13</v>
       </c>
@@ -5232,7 +5230,7 @@
       <c r="C86" s="26"/>
       <c r="D86" s="26"/>
     </row>
-    <row r="87" ht="20.4" spans="1:4">
+    <row r="87" ht="17.65" spans="1:4">
       <c r="A87" s="19" t="s">
         <v>46</v>
       </c>
@@ -5252,7 +5250,7 @@
       </c>
       <c r="D88" s="29"/>
     </row>
-    <row r="89" ht="20.4" spans="1:4">
+    <row r="89" ht="17.65" spans="1:4">
       <c r="A89" s="19" t="s">
         <v>48</v>
       </c>
@@ -5464,15 +5462,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H115"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="42.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.375" customWidth="1"/>
+    <col min="1" max="1" width="42.6283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1238938053097" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.3716814159292" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" spans="1:8">
+    <row r="1" ht="23" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -5489,7 +5487,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:8">
+    <row r="2" ht="20.65" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -5497,7 +5495,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" ht="20.4" spans="1:8">
+    <row r="3" ht="17.65" spans="1:8">
       <c r="A3" s="19" t="s">
         <v>46</v>
       </c>
@@ -5527,7 +5525,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" ht="51" spans="1:8">
+    <row r="6" ht="28.65" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>159</v>
       </c>
@@ -5541,7 +5539,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" ht="51" spans="1:8">
+    <row r="7" ht="28.65" spans="1:8">
       <c r="A7" s="16" t="s">
         <v>102</v>
       </c>
@@ -5555,7 +5553,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" ht="51" spans="1:8">
+    <row r="8" spans="1:8">
       <c r="A8" s="16" t="s">
         <v>105</v>
       </c>
@@ -5565,11 +5563,9 @@
       <c r="C8" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" ht="51" spans="1:8">
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" ht="28.65" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>114</v>
       </c>
@@ -5605,7 +5601,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" ht="17" spans="1:8">
+    <row r="12" ht="14.35" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>117</v>
       </c>
@@ -5619,7 +5615,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="1:8">
+    <row r="13" ht="14.35" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>120</v>
       </c>
@@ -5633,7 +5629,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:8">
+    <row r="14" ht="14.35" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>284</v>
       </c>
@@ -5647,7 +5643,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:8">
+    <row r="15" ht="14.35" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>131</v>
       </c>
@@ -5661,7 +5657,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" ht="17" spans="1:8">
+    <row r="16" ht="14.35" spans="1:8">
       <c r="A16" s="1" t="s">
         <v>133</v>
       </c>
@@ -5675,7 +5671,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" ht="17" spans="1:4">
+    <row r="17" ht="14.35" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>135</v>
       </c>
@@ -5689,7 +5685,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" ht="20.4" spans="1:4">
+    <row r="18" ht="17.65" spans="1:4">
       <c r="A18" s="19" t="s">
         <v>48</v>
       </c>
@@ -6104,7 +6100,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" ht="23.2" spans="1:4">
+    <row r="57" ht="20.65" spans="1:4">
       <c r="A57" s="25" t="s">
         <v>11</v>
       </c>
@@ -6112,7 +6108,7 @@
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
     </row>
-    <row r="58" ht="20.4" spans="1:4">
+    <row r="58" ht="17.65" spans="1:4">
       <c r="A58" s="19" t="s">
         <v>46</v>
       </c>
@@ -6131,7 +6127,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" ht="20.4" spans="1:4">
+    <row r="60" ht="17.65" spans="1:4">
       <c r="A60" s="19" t="s">
         <v>48</v>
       </c>
@@ -6524,7 +6520,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="97" ht="23.2" spans="1:4">
+    <row r="97" ht="20.65" spans="1:4">
       <c r="A97" s="26" t="s">
         <v>13</v>
       </c>
@@ -6532,7 +6528,7 @@
       <c r="C97" s="26"/>
       <c r="D97" s="26"/>
     </row>
-    <row r="98" ht="20.4" spans="1:4">
+    <row r="98" ht="17.65" spans="1:4">
       <c r="A98" s="19" t="s">
         <v>46</v>
       </c>
@@ -6552,7 +6548,7 @@
       </c>
       <c r="D99" s="29"/>
     </row>
-    <row r="100" ht="20.4" spans="1:4">
+    <row r="100" ht="17.65" spans="1:4">
       <c r="A100" s="19" t="s">
         <v>48</v>
       </c>
@@ -6749,15 +6745,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="42.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="42.6283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1238938053097" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.3716814159292" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" spans="1:8">
+    <row r="1" ht="23" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -6774,7 +6770,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:8">
+    <row r="2" ht="20.65" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -6782,7 +6778,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="18"/>
     </row>
-    <row r="3" ht="20.4" spans="1:8">
+    <row r="3" ht="17.65" spans="1:8">
       <c r="A3" s="19" t="s">
         <v>46</v>
       </c>
@@ -6790,7 +6786,7 @@
       <c r="C3" s="19"/>
       <c r="D3" s="20"/>
     </row>
-    <row r="4" ht="51" spans="1:8">
+    <row r="4" ht="28.65" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>299</v>
       </c>
@@ -6837,7 +6833,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" ht="68" spans="1:8">
+    <row r="8" ht="28.65" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>301</v>
       </c>
@@ -6851,7 +6847,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" ht="51" spans="1:8">
+    <row r="9" ht="28.65" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -6865,7 +6861,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="10" ht="17" spans="1:8">
+    <row r="10" ht="14.35" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>307</v>
       </c>
@@ -6879,7 +6875,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" ht="17" spans="1:8">
+    <row r="11" ht="14.35" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>309</v>
       </c>
@@ -6893,7 +6889,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" ht="20.4" spans="1:8">
+    <row r="12" ht="17.65" spans="1:8">
       <c r="A12" s="19" t="s">
         <v>48</v>
       </c>
@@ -7040,15 +7036,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="42.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.375" customWidth="1"/>
+    <col min="1" max="1" width="42.6283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1238938053097" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.3716814159292" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" spans="1:8">
+    <row r="1" ht="23" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -7065,7 +7061,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:8">
+    <row r="2" ht="20.65" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -7073,7 +7069,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="18"/>
     </row>
-    <row r="3" ht="20.4" spans="1:8">
+    <row r="3" ht="17.65" spans="1:8">
       <c r="A3" s="19" t="s">
         <v>46</v>
       </c>
@@ -7081,7 +7077,7 @@
       <c r="C3" s="19"/>
       <c r="D3" s="20"/>
     </row>
-    <row r="4" ht="17" spans="1:8">
+    <row r="4" ht="14.35" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>319</v>
       </c>
@@ -7095,7 +7091,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:8">
+    <row r="5" ht="14.35" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>321</v>
       </c>
@@ -7142,7 +7138,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="9" ht="51" spans="1:8">
+    <row r="9" ht="28.65" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>299</v>
       </c>
@@ -7156,7 +7152,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" ht="68" spans="1:8">
+    <row r="10" ht="43" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>327</v>
       </c>
@@ -7170,7 +7166,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="11" ht="20.4" spans="1:8">
+    <row r="11" ht="17.65" spans="1:8">
       <c r="A11" s="19" t="s">
         <v>48</v>
       </c>
@@ -7394,15 +7390,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="42.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.375" customWidth="1"/>
+    <col min="1" max="1" width="42.6283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1238938053097" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.3716814159292" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" spans="1:8">
+    <row r="1" ht="23" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -7419,7 +7415,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:8">
+    <row r="2" ht="20.65" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -7427,7 +7423,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="18"/>
     </row>
-    <row r="3" ht="20.4" spans="1:8">
+    <row r="3" ht="17.65" spans="1:8">
       <c r="A3" s="19" t="s">
         <v>46</v>
       </c>
@@ -7457,7 +7453,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" ht="84" spans="1:8">
+    <row r="6" ht="71.65" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>299</v>
       </c>
@@ -7471,7 +7467,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="7" ht="68" spans="1:8">
+    <row r="7" ht="43" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>327</v>
       </c>
@@ -7485,7 +7481,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:8">
+    <row r="8" ht="14.35" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>357</v>
       </c>
@@ -7499,7 +7495,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:8">
+    <row r="9" ht="14.35" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>359</v>
       </c>
@@ -7513,7 +7509,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" ht="17" spans="1:8">
+    <row r="10" ht="14.35" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>361</v>
       </c>
@@ -7527,7 +7523,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" ht="17" spans="1:8">
+    <row r="11" ht="14.35" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>363</v>
       </c>
@@ -7541,7 +7537,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" ht="20.4" spans="1:8">
+    <row r="12" ht="17.65" spans="1:8">
       <c r="A12" s="19" t="s">
         <v>48</v>
       </c>
@@ -7743,12 +7739,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="42.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="42.6283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1238938053097" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.3716814159292" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:8">
@@ -7769,7 +7765,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="23.2" spans="1:8">
+    <row r="2" ht="20.65" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -7777,7 +7773,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" ht="20.4" spans="1:8">
+    <row r="3" ht="17.65" spans="1:8">
       <c r="A3" s="9" t="s">
         <v>46</v>
       </c>
@@ -7785,7 +7781,7 @@
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
     </row>
-    <row r="4" ht="51" spans="1:8">
+    <row r="4" ht="28.65" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>374</v>
       </c>
@@ -7799,7 +7795,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:8">
+    <row r="5" ht="14.35" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>377</v>
       </c>
@@ -7813,7 +7809,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:8">
+    <row r="6" ht="14.35" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>379</v>
       </c>
@@ -7827,7 +7823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" ht="20.4" spans="1:8">
+    <row r="7" ht="17.65" spans="1:8">
       <c r="A7" s="12" t="s">
         <v>48</v>
       </c>
@@ -7934,7 +7930,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="18" ht="23.2" spans="1:4">
+    <row r="18" ht="20.65" spans="1:4">
       <c r="A18" s="8" t="s">
         <v>31</v>
       </c>
@@ -7942,7 +7938,7 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" ht="20.4" spans="1:4">
+    <row r="19" ht="17.65" spans="1:4">
       <c r="A19" s="9" t="s">
         <v>46</v>
       </c>
@@ -7961,7 +7957,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" ht="20.4" spans="1:4">
+    <row r="21" ht="17.65" spans="1:4">
       <c r="A21" s="12" t="s">
         <v>48</v>
       </c>
@@ -8013,7 +8009,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="27" ht="23.2" spans="1:4">
+    <row r="27" ht="20.65" spans="1:4">
       <c r="A27" s="8" t="s">
         <v>33</v>
       </c>
@@ -8021,7 +8017,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
     </row>
-    <row r="28" ht="20.4" spans="1:4">
+    <row r="28" ht="17.65" spans="1:4">
       <c r="A28" s="9" t="s">
         <v>46</v>
       </c>
@@ -8034,7 +8030,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" ht="20.4" spans="1:4">
+    <row r="30" ht="17.65" spans="1:4">
       <c r="A30" s="12" t="s">
         <v>48</v>
       </c>
@@ -8042,7 +8038,7 @@
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" ht="14.3" customHeight="1" spans="1:4">
+    <row r="31" customHeight="1" spans="1:4">
       <c r="A31" s="1" t="s">
         <v>402</v>
       </c>
@@ -8053,13 +8049,13 @@
         <v>403</v>
       </c>
     </row>
-    <row r="32" ht="14.3" customHeight="1" spans="1:4">
+    <row r="32" customHeight="1" spans="1:4">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" ht="23.2" spans="1:4">
+    <row r="33" ht="20.65" spans="1:4">
       <c r="A33" s="8" t="s">
         <v>35</v>
       </c>
@@ -8067,7 +8063,7 @@
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" ht="20.4" spans="1:4">
+    <row r="34" ht="17.65" spans="1:4">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
@@ -8086,7 +8082,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="36" ht="20.4" spans="1:4">
+    <row r="36" ht="17.65" spans="1:4">
       <c r="A36" s="12" t="s">
         <v>48</v>
       </c>
@@ -8099,7 +8095,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" ht="23.2" spans="1:4">
+    <row r="39" ht="20.65" spans="1:4">
       <c r="A39" s="8" t="s">
         <v>37</v>
       </c>
@@ -8107,7 +8103,7 @@
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
     </row>
-    <row r="40" ht="20.4" spans="1:4">
+    <row r="40" ht="17.65" spans="1:4">
       <c r="A40" s="9" t="s">
         <v>46</v>
       </c>
@@ -8120,7 +8116,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" ht="20.4" spans="1:4">
+    <row r="42" ht="17.65" spans="1:4">
       <c r="A42" s="12" t="s">
         <v>48</v>
       </c>
@@ -8216,7 +8212,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="52" ht="23.2" spans="1:4">
+    <row r="52" ht="20.65" spans="1:4">
       <c r="A52" s="8" t="s">
         <v>39</v>
       </c>
@@ -8224,7 +8220,7 @@
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" ht="20.4" spans="1:4">
+    <row r="53" ht="17.65" spans="1:4">
       <c r="A53" s="9" t="s">
         <v>46</v>
       </c>
@@ -8232,7 +8228,7 @@
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
     </row>
-    <row r="54" ht="14.3" customHeight="1" spans="1:4">
+    <row r="54" customHeight="1" spans="1:4">
       <c r="A54" s="16" t="s">
         <v>139</v>
       </c>
@@ -8277,7 +8273,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="58" ht="84" spans="1:4">
+    <row r="58" ht="57.35" spans="1:4">
       <c r="A58" s="16" t="s">
         <v>414</v>
       </c>
@@ -8302,7 +8298,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="60" ht="20.4" spans="1:4">
+    <row r="60" ht="17.65" spans="1:4">
       <c r="A60" s="12" t="s">
         <v>48</v>
       </c>
@@ -8310,7 +8306,7 @@
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
     </row>
-    <row r="61" ht="17" spans="1:4">
+    <row r="61" ht="14.35" spans="1:4">
       <c r="A61" s="1" t="s">
         <v>417</v>
       </c>
